--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5821,25 +5821,25 @@
         <v>46235</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>48.232912</v>
+        <v>48.232591</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>0.029301</v>
+        <v>0.028979</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.608084</v>
+        <v>-0.6087360000000001</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>47.997733</v>
+        <v>47.906168</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>47.498528</v>
+        <v>47.326085</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>48.000377</v>
+        <v>48.200312</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>48.608038</v>
+        <v>48.582329</v>
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
@@ -5857,6 +5857,57 @@
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>1 de septiembre de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>48.342018</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>0.109427</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>0.188664</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>47.882252</v>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>47.76499</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>48.881224</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>48.395132</v>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K110" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M110" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>

--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf · Fecha de publicación: 1 de septiembre de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf · Fecha de publicación: 1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3099,12 +3099,12 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M58" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3303,12 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3354,12 +3354,12 @@
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3507,12 +3507,12 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3762,12 +3762,12 @@
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4068,12 @@
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4119,12 +4119,12 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M76" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4578,12 @@
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4680,12 +4680,12 @@
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4884,12 @@
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5190,12 +5190,12 @@
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5292,12 +5292,12 @@
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5343,12 +5343,12 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="L100" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5445,12 +5445,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="L102" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5547,12 +5547,12 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5649,12 +5649,12 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5700,12 +5700,12 @@
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5751,12 +5751,12 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_10.pdf</t>
         </is>
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>1 de septiembre de 2026</t>
+          <t>1 de octubre de 2026</t>
         </is>
       </c>
     </row>
